--- a/data/科室诊疗量对比分析_专业报告.xlsx
+++ b/data/科室诊疗量对比分析_专业报告.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-        <bgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,8 +108,8 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3759,116 +3759,116 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>耳鼻喉科</t>
+          <t>推拿一科</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>510089</v>
+        <v>2474713</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1064488</v>
+        <v>2500621</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>554399</v>
+        <v>25908</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>108.69</v>
+        <v>1.05</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>→基本持平</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>推拿二科</t>
+          <t>儿科</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1013798</v>
+        <v>2057402</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1404839</v>
+        <v>2032695</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>391041</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>38.57</v>
+        <v>-24707</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.2</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>→基本持平</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>骨伤科</t>
+          <t>眼科</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>853410</v>
+        <v>1424849</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1183685</v>
+        <v>1515010</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>330275</v>
+        <v>90161</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>38.7</v>
+        <v>6.33</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>↑小幅增长</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>乳腺病科</t>
+          <t>推拿二科</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>521007</v>
+        <v>1013798</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>650278</v>
+        <v>1404839</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>129271</v>
+        <v>391041</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>24.81</v>
+        <v>38.57</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>↑小幅增长</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>皮肤科</t>
+          <t>骨伤科</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>278000</v>
+        <v>853410</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>374675</v>
+        <v>1183685</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>96675</v>
+        <v>330275</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>34.78</v>
+        <v>38.7</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3879,526 +3879,526 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>眼科</t>
+          <t>耳鼻喉科</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1424849</v>
+        <v>510089</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1515010</v>
+        <v>1064488</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>90161</v>
+        <v>554399</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.33</v>
+        <v>108.69</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>↑小幅增长</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>儿童康复门诊</t>
+          <t>乳腺病科</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>521007</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>74514</v>
+        <v>650278</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>74514</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>∞ (新增/归零)</t>
-        </is>
+        <v>129271</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>24.81</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>🚀 新增业务↑</t>
+          <t>↑小幅增长</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>康复中心</t>
+          <t>治未病中心</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12659</v>
+        <v>696169</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>71384</v>
+        <v>578929</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58725</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>463.9</v>
+        <v>-117240</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-16.84</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>内分泌科</t>
+          <t>不孕不育科</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>41562</v>
+        <v>1107730</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>90643.42999999999</v>
+        <v>520581</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>49081.42999999999</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>118.09</v>
+        <v>-587149</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-53</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>推拿一科</t>
+          <t>脾胃病科</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2474713</v>
+        <v>505996</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2500621</v>
+        <v>441631</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25908</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1.05</v>
+        <v>-64365</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-12.72</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>→基本持平</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>周围血管病科</t>
+          <t>脑病科</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>53086</v>
+        <v>396889</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>78680</v>
+        <v>377538</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>25594</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>48.21</v>
+        <v>-19351</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-4.88</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>→基本持平</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>康复科</t>
+          <t>皮肤科</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>88645</v>
+        <v>278000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>110957</v>
+        <v>374675</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22312</v>
+        <v>96675</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>25.17</v>
+        <v>34.78</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>↑小幅增长</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>肿瘤科</t>
+          <t>妇产科</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9150</v>
+        <v>438409</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>12433</v>
+        <v>361499</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3283</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>35.88</v>
+        <v>-76910</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-17.54</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>↑显著增长</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>肛肠一科</t>
+          <t>男科</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>6544</v>
+        <v>450721</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7353</v>
+        <v>243848</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>809</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>12.36</v>
+        <v>-206873</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-45.9</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>↑小幅增长</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>肝病科</t>
+          <t>康复科</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>30</v>
+        <v>88645</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>110957</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>-100</v>
+        <v>22312</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>25.17</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↑小幅增长</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>咳嗽门诊</t>
+          <t>急诊科</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1248</v>
+        <v>129142</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>108977</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1248</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-100</v>
+        <v>-20165</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-15.61</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>肺病科</t>
+          <t>内分泌科</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>22944</v>
+        <v>41562</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>21624</v>
+        <v>90643.42999999999</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-1320</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>-5.75</v>
+        <v>49081.42999999999</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>118.09</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>口腔科</t>
+          <t>周围血管病科</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1672</v>
+        <v>53086</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>165</v>
+        <v>78680</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-1507</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-90.13</v>
+        <v>25594</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>48.21</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>三部六病</t>
+          <t>儿童康复门诊</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11809</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8466</v>
+        <v>74514</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-3343</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>-28.31</v>
+        <v>74514</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>∞ (新增/归零)</t>
+        </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>🚀 新增业务↑</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>肛肠二科</t>
+          <t>康复中心</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>18173</v>
+        <v>12659</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>12422</v>
+        <v>71384</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-5751</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>-31.65</v>
+        <v>58725</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>463.9</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>肾病科</t>
+          <t>心血管病中心</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>39284</v>
+        <v>159468</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>32178</v>
+        <v>66869</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-7106</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>-18.09</v>
+        <v>-92599</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-58.07</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>外科</t>
+          <t>肾病科</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8671</v>
+        <v>39284</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>750</v>
+        <v>32178</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-7921</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>-91.34999999999999</v>
+        <v>-7106</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-18.09</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>经方研究室</t>
+          <t>肺病科</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>23840</v>
+        <v>22944</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12600</v>
+        <v>21624</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11240</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>-47.15</v>
+        <v>-1320</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-5.75</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>↓大幅下降</t>
+          <t>↓小幅下降</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>脑病科</t>
+          <t>经方研究室</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>396889</v>
+        <v>23840</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>377538</v>
+        <v>12600</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-19351</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>-4.88</v>
+        <v>-11240</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-47.15</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>→基本持平</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>急诊科</t>
+          <t>肿瘤科</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>129142</v>
+        <v>9150</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>108977</v>
+        <v>12433</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-20165</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>-15.61</v>
+        <v>3283</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>35.88</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>↑显著增长</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>儿科</t>
+          <t>肛肠二科</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2057402</v>
+        <v>18173</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2032695</v>
+        <v>12422</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-24707</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>-1.2</v>
+        <v>-5751</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-31.65</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>→基本持平</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>脾胃病科</t>
+          <t>三部六病</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>505996</v>
+        <v>11809</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>441631</v>
+        <v>8466</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-64365</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>-12.72</v>
+        <v>-3343</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>-28.31</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -4409,44 +4409,44 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>妇产科</t>
+          <t>肛肠一科</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>438409</v>
+        <v>6544</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>361499</v>
+        <v>7353</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-76910</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>-17.54</v>
+        <v>809</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>12.36</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>↑小幅增长</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>心血管病中心</t>
+          <t>外科</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>159468</v>
+        <v>8671</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>66869</v>
+        <v>750</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-92599</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>-58.07</v>
+        <v>-7921</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>-91.34999999999999</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -4457,44 +4457,44 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>治未病中心</t>
+          <t>口腔科</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>696169</v>
+        <v>1672</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>578929</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-117240</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>-16.84</v>
+        <v>-1507</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-90.13</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>↓小幅下降</t>
+          <t>↓大幅下降</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>男科</t>
+          <t>咳嗽门诊</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>450721</v>
+        <v>1248</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>243848</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-206873</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>-45.9</v>
+        <v>-1248</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-100</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -4505,20 +4505,20 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>不孕不育科</t>
+          <t>肝病科</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1107730</v>
+        <v>30</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>520581</v>
+        <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-587149</v>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>-53</v>
+        <v>-30</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>-100</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
       <c r="E4" s="3" t="n">
         <v>-155</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="5" t="n">
         <v>-15.66</v>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       <c r="E5" s="3" t="n">
         <v>-1002</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>-59.57</v>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       <c r="E6" s="3" t="n">
         <v>-333</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>-35.24</v>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="E7" s="3" t="n">
         <v>-328</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>-28.67</v>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       <c r="E8" s="3" t="n">
         <v>-193</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>-16.71</v>
       </c>
     </row>
@@ -4792,7 +4792,7 @@
       <c r="E10" s="3" t="n">
         <v>-365</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>-41.48</v>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       <c r="E11" s="3" t="n">
         <v>-417</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>-60.43</v>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       <c r="E12" s="3" t="n">
         <v>-899</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>-79.34999999999999</v>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="E13" s="3" t="n">
         <v>-516</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="5" t="n">
         <v>-52.12</v>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       <c r="E16" s="3" t="n">
         <v>-46844</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="5" t="n">
         <v>-44.91</v>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="E17" s="3" t="n">
         <v>-82737</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>-68.11</v>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       <c r="E18" s="3" t="n">
         <v>-82855</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="5" t="n">
         <v>-76.43000000000001</v>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       <c r="E19" s="3" t="n">
         <v>-65240</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="5" t="n">
         <v>-64.05</v>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       <c r="E20" s="3" t="n">
         <v>-50935</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="5" t="n">
         <v>-46.41</v>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       <c r="E21" s="3" t="n">
         <v>-62701</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>-57.31</v>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       <c r="E22" s="3" t="n">
         <v>-56193</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="5" t="n">
         <v>-56.61</v>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       <c r="E23" s="3" t="n">
         <v>-40743</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="5" t="n">
         <v>-52.88</v>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       <c r="E24" s="3" t="n">
         <v>-61924</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="5" t="n">
         <v>-68.16</v>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       <c r="E25" s="3" t="n">
         <v>-55777</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="5" t="n">
         <v>-59.28</v>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       <c r="E38" s="3" t="n">
         <v>-20225</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="5" t="n">
         <v>-13.33</v>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       <c r="E42" s="3" t="n">
         <v>-14307</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="5" t="n">
         <v>-9.32</v>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       <c r="E43" s="3" t="n">
         <v>-7133</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="5" t="n">
         <v>-4.6</v>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       <c r="E44" s="3" t="n">
         <v>-33384</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="5" t="n">
         <v>-11.54</v>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       <c r="E47" s="3" t="n">
         <v>-16108</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="5" t="n">
         <v>-10.89</v>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       <c r="E48" s="3" t="n">
         <v>-28516</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="5" t="n">
         <v>-10.7</v>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       <c r="E49" s="3" t="n">
         <v>-76294</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="5" t="n">
         <v>-29.26</v>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       <c r="E53" s="3" t="n">
         <v>6802</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5856,7 +5856,7 @@
       <c r="E54" s="3" t="n">
         <v>2272</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5882,7 +5882,7 @@
       <c r="E55" s="3" t="n">
         <v>4060</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5908,7 +5908,7 @@
       <c r="E56" s="3" t="n">
         <v>18282</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5934,7 +5934,7 @@
       <c r="E57" s="3" t="n">
         <v>13073</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5960,7 +5960,7 @@
       <c r="E58" s="3" t="n">
         <v>8761</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -5986,7 +5986,7 @@
       <c r="E59" s="3" t="n">
         <v>9662</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -6012,7 +6012,7 @@
       <c r="E60" s="3" t="n">
         <v>6730</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -6038,7 +6038,7 @@
       <c r="E61" s="3" t="n">
         <v>4872</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -6352,7 +6352,7 @@
       <c r="E74" s="3" t="n">
         <v>-1254</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="5" t="n">
         <v>-58.06</v>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       <c r="E75" s="3" t="n">
         <v>-1560</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="5" t="n">
         <v>-54.17</v>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       <c r="E76" s="3" t="n">
         <v>-701.9000000000001</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="5" t="n">
         <v>-14.81</v>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       <c r="E89" s="3" t="n">
         <v>-330</v>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="F89" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       <c r="E91" s="3" t="n">
         <v>-742</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       <c r="E92" s="3" t="n">
         <v>-600</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       <c r="E95" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7138,7 +7138,7 @@
       <c r="E106" s="3" t="n">
         <v>-2129</v>
       </c>
-      <c r="F106" s="6" t="n">
+      <c r="F106" s="5" t="n">
         <v>-25.12</v>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       <c r="E110" s="3" t="n">
         <v>-1056</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="F110" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       <c r="E112" s="3" t="n">
         <v>-192</v>
       </c>
-      <c r="F112" s="6" t="n">
+      <c r="F112" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
       <c r="E122" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7568,7 +7568,7 @@
       <c r="E123" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7594,7 +7594,7 @@
       <c r="E124" s="3" t="n">
         <v>-154</v>
       </c>
-      <c r="F124" s="6" t="n">
+      <c r="F124" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       <c r="E125" s="3" t="n">
         <v>-110</v>
       </c>
-      <c r="F125" s="6" t="n">
+      <c r="F125" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       <c r="E127" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7718,7 +7718,7 @@
       <c r="E129" s="3" t="n">
         <v>-2650</v>
       </c>
-      <c r="F129" s="6" t="n">
+      <c r="F129" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       <c r="E130" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7768,7 +7768,7 @@
       <c r="E131" s="3" t="n">
         <v>-1368</v>
       </c>
-      <c r="F131" s="6" t="n">
+      <c r="F131" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       <c r="E132" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -7818,7 +7818,7 @@
       <c r="E133" s="3" t="n">
         <v>-4114</v>
       </c>
-      <c r="F133" s="6" t="n">
+      <c r="F133" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="E136" s="3" t="n">
         <v>-36927</v>
       </c>
-      <c r="F136" s="6" t="n">
+      <c r="F136" s="5" t="n">
         <v>-53.39</v>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       <c r="E137" s="3" t="n">
         <v>-35681</v>
       </c>
-      <c r="F137" s="6" t="n">
+      <c r="F137" s="5" t="n">
         <v>-60.75</v>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       <c r="E140" s="3" t="n">
         <v>-7076</v>
       </c>
-      <c r="F140" s="6" t="n">
+      <c r="F140" s="5" t="n">
         <v>-15.62</v>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       <c r="E141" s="3" t="n">
         <v>-9061</v>
       </c>
-      <c r="F141" s="6" t="n">
+      <c r="F141" s="5" t="n">
         <v>-22.48</v>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       <c r="E143" s="3" t="n">
         <v>-12845</v>
       </c>
-      <c r="F143" s="6" t="n">
+      <c r="F143" s="5" t="n">
         <v>-38.75</v>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       <c r="E144" s="3" t="n">
         <v>-9739</v>
       </c>
-      <c r="F144" s="6" t="n">
+      <c r="F144" s="5" t="n">
         <v>-36.1</v>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       <c r="E145" s="3" t="n">
         <v>-6115</v>
       </c>
-      <c r="F145" s="6" t="n">
+      <c r="F145" s="5" t="n">
         <v>-19.64</v>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       <c r="E146" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="F146" s="5" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -8156,7 +8156,7 @@
       <c r="E147" s="3" t="n">
         <v>-760</v>
       </c>
-      <c r="F147" s="6" t="n">
+      <c r="F147" s="5" t="n">
         <v>-58.28</v>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="E155" s="3" t="n">
         <v>-492</v>
       </c>
-      <c r="F155" s="6" t="n">
+      <c r="F155" s="5" t="n">
         <v>-31.5</v>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       <c r="E156" s="3" t="n">
         <v>-50</v>
       </c>
-      <c r="F156" s="6" t="n">
+      <c r="F156" s="5" t="n">
         <v>-4.74</v>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       <c r="E157" s="3" t="n">
         <v>-510</v>
       </c>
-      <c r="F157" s="6" t="n">
+      <c r="F157" s="5" t="n">
         <v>-47.22</v>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       <c r="E164" s="3" t="n">
         <v>-3516</v>
       </c>
-      <c r="F164" s="6" t="n">
+      <c r="F164" s="5" t="n">
         <v>-23.32</v>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       <c r="E165" s="3" t="n">
         <v>-4630</v>
       </c>
-      <c r="F165" s="6" t="n">
+      <c r="F165" s="5" t="n">
         <v>-34.52</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="E166" s="3" t="n">
         <v>-939</v>
       </c>
-      <c r="F166" s="6" t="n">
+      <c r="F166" s="5" t="n">
         <v>-11.65</v>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="E168" s="3" t="n">
         <v>-5374</v>
       </c>
-      <c r="F168" s="6" t="n">
+      <c r="F168" s="5" t="n">
         <v>-57.86</v>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       <c r="E169" s="3" t="n">
         <v>-3141</v>
       </c>
-      <c r="F169" s="6" t="n">
+      <c r="F169" s="5" t="n">
         <v>-23.72</v>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       <c r="E171" s="3" t="n">
         <v>-671</v>
       </c>
-      <c r="F171" s="6" t="n">
+      <c r="F171" s="5" t="n">
         <v>-16.73</v>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       <c r="E174" s="3" t="n">
         <v>-6702</v>
       </c>
-      <c r="F174" s="6" t="n">
+      <c r="F174" s="5" t="n">
         <v>-44.66</v>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       <c r="E175" s="3" t="n">
         <v>-13259</v>
       </c>
-      <c r="F175" s="6" t="n">
+      <c r="F175" s="5" t="n">
         <v>-65.64</v>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       <c r="E176" s="3" t="n">
         <v>-48813</v>
       </c>
-      <c r="F176" s="6" t="n">
+      <c r="F176" s="5" t="n">
         <v>-81.48</v>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       <c r="E177" s="3" t="n">
         <v>-7942</v>
       </c>
-      <c r="F177" s="6" t="n">
+      <c r="F177" s="5" t="n">
         <v>-65.5</v>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       <c r="E178" s="3" t="n">
         <v>-4982</v>
       </c>
-      <c r="F178" s="6" t="n">
+      <c r="F178" s="5" t="n">
         <v>-78.15000000000001</v>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
       <c r="E179" s="3" t="n">
         <v>-2861</v>
       </c>
-      <c r="F179" s="6" t="n">
+      <c r="F179" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       <c r="E180" s="3" t="n">
         <v>-5475</v>
       </c>
-      <c r="F180" s="6" t="n">
+      <c r="F180" s="5" t="n">
         <v>-78.73999999999999</v>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       <c r="E181" s="3" t="n">
         <v>-11297</v>
       </c>
-      <c r="F181" s="6" t="n">
+      <c r="F181" s="5" t="n">
         <v>-91.56</v>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       <c r="E183" s="3" t="n">
         <v>-4169</v>
       </c>
-      <c r="F183" s="6" t="n">
+      <c r="F183" s="5" t="n">
         <v>-43.5</v>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       <c r="E185" s="3" t="n">
         <v>-6100</v>
       </c>
-      <c r="F185" s="6" t="n">
+      <c r="F185" s="5" t="n">
         <v>-49.7</v>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       <c r="E186" s="3" t="n">
         <v>-7345</v>
       </c>
-      <c r="F186" s="6" t="n">
+      <c r="F186" s="5" t="n">
         <v>-57.24</v>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       <c r="E187" s="3" t="n">
         <v>-8448</v>
       </c>
-      <c r="F187" s="6" t="n">
+      <c r="F187" s="5" t="n">
         <v>-63.99</v>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       <c r="E188" s="3" t="n">
         <v>-5915</v>
       </c>
-      <c r="F188" s="6" t="n">
+      <c r="F188" s="5" t="n">
         <v>-44.28</v>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       <c r="E189" s="3" t="n">
         <v>-3637</v>
       </c>
-      <c r="F189" s="6" t="n">
+      <c r="F189" s="5" t="n">
         <v>-38.06</v>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       <c r="E190" s="3" t="n">
         <v>-9684</v>
       </c>
-      <c r="F190" s="6" t="n">
+      <c r="F190" s="5" t="n">
         <v>-60.55</v>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       <c r="E191" s="3" t="n">
         <v>-1589</v>
       </c>
-      <c r="F191" s="6" t="n">
+      <c r="F191" s="5" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       <c r="E194" s="3" t="n">
         <v>-5488</v>
       </c>
-      <c r="F194" s="6" t="n">
+      <c r="F194" s="5" t="n">
         <v>-2.39</v>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       <c r="E196" s="3" t="n">
         <v>-1310</v>
       </c>
-      <c r="F196" s="6" t="n">
+      <c r="F196" s="5" t="n">
         <v>-0.72</v>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       <c r="E197" s="3" t="n">
         <v>-7996</v>
       </c>
-      <c r="F197" s="6" t="n">
+      <c r="F197" s="5" t="n">
         <v>-3.78</v>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
       <c r="E200" s="3" t="n">
         <v>-52907</v>
       </c>
-      <c r="F200" s="6" t="n">
+      <c r="F200" s="5" t="n">
         <v>-18.49</v>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       <c r="E203" s="3" t="n">
         <v>-16358</v>
       </c>
-      <c r="F203" s="6" t="n">
+      <c r="F203" s="5" t="n">
         <v>-9.08</v>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       <c r="E204" s="3" t="n">
         <v>-47743</v>
       </c>
-      <c r="F204" s="6" t="n">
+      <c r="F204" s="5" t="n">
         <v>-19.4</v>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
       <c r="E205" s="3" t="n">
         <v>-16920</v>
       </c>
-      <c r="F205" s="6" t="n">
+      <c r="F205" s="5" t="n">
         <v>-6.76</v>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       <c r="E206" s="3" t="n">
         <v>-16941</v>
       </c>
-      <c r="F206" s="6" t="n">
+      <c r="F206" s="5" t="n">
         <v>-19.1</v>
       </c>
     </row>
@@ -9908,7 +9908,7 @@
       <c r="E220" s="3" t="n">
         <v>-1209</v>
       </c>
-      <c r="F220" s="6" t="n">
+      <c r="F220" s="5" t="n">
         <v>-4.43</v>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
       <c r="E221" s="3" t="n">
         <v>-5667</v>
       </c>
-      <c r="F221" s="6" t="n">
+      <c r="F221" s="5" t="n">
         <v>-17.44</v>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       <c r="E222" s="3" t="n">
         <v>-14232</v>
       </c>
-      <c r="F222" s="6" t="n">
+      <c r="F222" s="5" t="n">
         <v>-42.42</v>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       <c r="E223" s="3" t="n">
         <v>-3561</v>
       </c>
-      <c r="F223" s="6" t="n">
+      <c r="F223" s="5" t="n">
         <v>-4.07</v>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       <c r="E224" s="3" t="n">
         <v>-27379</v>
       </c>
-      <c r="F224" s="6" t="n">
+      <c r="F224" s="5" t="n">
         <v>-9.31</v>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       <c r="E225" s="3" t="n">
         <v>-11906</v>
       </c>
-      <c r="F225" s="6" t="n">
+      <c r="F225" s="5" t="n">
         <v>-25.87</v>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       <c r="E226" s="3" t="n">
         <v>-6887</v>
       </c>
-      <c r="F226" s="6" t="n">
+      <c r="F226" s="5" t="n">
         <v>-36.78</v>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       <c r="E227" s="3" t="n">
         <v>-2982</v>
       </c>
-      <c r="F227" s="6" t="n">
+      <c r="F227" s="5" t="n">
         <v>-15.79</v>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       <c r="E228" s="3" t="n">
         <v>-61293</v>
       </c>
-      <c r="F228" s="6" t="n">
+      <c r="F228" s="5" t="n">
         <v>-77.95999999999999</v>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       <c r="E229" s="3" t="n">
         <v>-14507</v>
       </c>
-      <c r="F229" s="6" t="n">
+      <c r="F229" s="5" t="n">
         <v>-34.77</v>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       <c r="E230" s="3" t="n">
         <v>-63776</v>
       </c>
-      <c r="F230" s="6" t="n">
+      <c r="F230" s="5" t="n">
         <v>-72.33</v>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       <c r="E231" s="3" t="n">
         <v>-11863</v>
       </c>
-      <c r="F231" s="6" t="n">
+      <c r="F231" s="5" t="n">
         <v>-35.18</v>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       <c r="E232" s="3" t="n">
         <v>-18632</v>
       </c>
-      <c r="F232" s="6" t="n">
+      <c r="F232" s="5" t="n">
         <v>-43.32</v>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       <c r="E233" s="3" t="n">
         <v>-784</v>
       </c>
-      <c r="F233" s="6" t="n">
+      <c r="F233" s="5" t="n">
         <v>-2.74</v>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       <c r="E234" s="3" t="n">
         <v>-11138</v>
       </c>
-      <c r="F234" s="6" t="n">
+      <c r="F234" s="5" t="n">
         <v>-34.64</v>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       <c r="E235" s="3" t="n">
         <v>-4299</v>
       </c>
-      <c r="F235" s="6" t="n">
+      <c r="F235" s="5" t="n">
         <v>-17.03</v>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       <c r="E236" s="3" t="n">
         <v>-12618</v>
       </c>
-      <c r="F236" s="6" t="n">
+      <c r="F236" s="5" t="n">
         <v>-38.74</v>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       <c r="E237" s="3" t="n">
         <v>-16388</v>
       </c>
-      <c r="F237" s="6" t="n">
+      <c r="F237" s="5" t="n">
         <v>-49.46</v>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       <c r="E238" s="3" t="n">
         <v>-18328</v>
       </c>
-      <c r="F238" s="6" t="n">
+      <c r="F238" s="5" t="n">
         <v>-56.64</v>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       <c r="E239" s="3" t="n">
         <v>-11247</v>
       </c>
-      <c r="F239" s="6" t="n">
+      <c r="F239" s="5" t="n">
         <v>-40.79</v>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       <c r="E240" s="3" t="n">
         <v>-19067</v>
       </c>
-      <c r="F240" s="6" t="n">
+      <c r="F240" s="5" t="n">
         <v>-55.37</v>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       <c r="E241" s="3" t="n">
         <v>-18733</v>
       </c>
-      <c r="F241" s="6" t="n">
+      <c r="F241" s="5" t="n">
         <v>-47.13</v>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       <c r="E244" s="3" t="n">
         <v>-3739</v>
       </c>
-      <c r="F244" s="6" t="n">
+      <c r="F244" s="5" t="n">
         <v>-15.13</v>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       <c r="E245" s="3" t="n">
         <v>-7302</v>
       </c>
-      <c r="F245" s="6" t="n">
+      <c r="F245" s="5" t="n">
         <v>-35.85</v>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       <c r="E246" s="3" t="n">
         <v>-7676</v>
       </c>
-      <c r="F246" s="6" t="n">
+      <c r="F246" s="5" t="n">
         <v>-35.68</v>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       <c r="E247" s="3" t="n">
         <v>-8271</v>
       </c>
-      <c r="F247" s="6" t="n">
+      <c r="F247" s="5" t="n">
         <v>-24.66</v>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       <c r="E254" s="3" t="n">
         <v>-18686</v>
       </c>
-      <c r="F254" s="6" t="n">
+      <c r="F254" s="5" t="n">
         <v>-16.07</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       <c r="E256" s="3" t="n">
         <v>-10040</v>
       </c>
-      <c r="F256" s="6" t="n">
+      <c r="F256" s="5" t="n">
         <v>-6.61</v>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       <c r="E257" s="3" t="n">
         <v>-25549</v>
       </c>
-      <c r="F257" s="6" t="n">
+      <c r="F257" s="5" t="n">
         <v>-16.37</v>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       <c r="E263" s="3" t="n">
         <v>-47</v>
       </c>
-      <c r="F263" s="6" t="n">
+      <c r="F263" s="5" t="n">
         <v>-0.05</v>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       <c r="E266" s="3" t="n">
         <v>-96</v>
       </c>
-      <c r="F266" s="6" t="n">
+      <c r="F266" s="5" t="n">
         <v>-13.33</v>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       <c r="E267" s="3" t="n">
         <v>-1416</v>
       </c>
-      <c r="F267" s="6" t="n">
+      <c r="F267" s="5" t="n">
         <v>-65.56</v>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       <c r="E268" s="3" t="n">
         <v>-2184</v>
       </c>
-      <c r="F268" s="6" t="n">
+      <c r="F268" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       <c r="E269" s="3" t="n">
         <v>-2104</v>
       </c>
-      <c r="F269" s="6" t="n">
+      <c r="F269" s="5" t="n">
         <v>-66.92</v>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       <c r="E272" s="3" t="n">
         <v>-7928</v>
       </c>
-      <c r="F272" s="6" t="n">
+      <c r="F272" s="5" t="n">
         <v>-87.62</v>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       <c r="E276" s="3" t="n">
         <v>-18</v>
       </c>
-      <c r="F276" s="6" t="n">
+      <c r="F276" s="5" t="n">
         <v>-3.75</v>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       <c r="E277" s="3" t="n">
         <v>-1832</v>
       </c>
-      <c r="F277" s="6" t="n">
+      <c r="F277" s="5" t="n">
         <v>-65.62</v>
       </c>
     </row>
@@ -11588,7 +11588,7 @@
       <c r="E290" s="3" t="n">
         <v>-110</v>
       </c>
-      <c r="F290" s="6" t="n">
+      <c r="F290" s="5" t="n">
         <v>-42.31</v>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       <c r="E291" s="3" t="n">
         <v>1244</v>
       </c>
-      <c r="F291" s="5" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -11638,7 +11638,7 @@
       <c r="E292" s="3" t="n">
         <v>-480</v>
       </c>
-      <c r="F292" s="6" t="n">
+      <c r="F292" s="5" t="n">
         <v>-86.33</v>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       <c r="E295" s="3" t="n">
         <v>-204</v>
       </c>
-      <c r="F295" s="6" t="n">
+      <c r="F295" s="5" t="n">
         <v>-19.62</v>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       <c r="E296" s="3" t="n">
         <v>-723</v>
       </c>
-      <c r="F296" s="6" t="n">
+      <c r="F296" s="5" t="n">
         <v>-69.52</v>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       <c r="E298" s="3" t="n">
         <v>-1142</v>
       </c>
-      <c r="F298" s="6" t="n">
+      <c r="F298" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       <c r="E299" s="3" t="n">
         <v>-46</v>
       </c>
-      <c r="F299" s="6" t="n">
+      <c r="F299" s="5" t="n">
         <v>-6.87</v>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       <c r="E302" s="3" t="n">
         <v>-832</v>
       </c>
-      <c r="F302" s="6" t="n">
+      <c r="F302" s="5" t="n">
         <v>-65.67</v>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       <c r="E303" s="3" t="n">
         <v>-2472</v>
       </c>
-      <c r="F303" s="6" t="n">
+      <c r="F303" s="5" t="n">
         <v>-97.78</v>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       <c r="E306" s="3" t="n">
         <v>-1664</v>
       </c>
-      <c r="F306" s="6" t="n">
+      <c r="F306" s="5" t="n">
         <v>-98.45999999999999</v>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       <c r="E307" s="3" t="n">
         <v>-1238</v>
       </c>
-      <c r="F307" s="6" t="n">
+      <c r="F307" s="5" t="n">
         <v>-60.75</v>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
       <c r="E309" s="3" t="n">
         <v>-1046</v>
       </c>
-      <c r="F309" s="6" t="n">
+      <c r="F309" s="5" t="n">
         <v>-49.06</v>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       <c r="E311" s="3" t="n">
         <v>-1728</v>
       </c>
-      <c r="F311" s="6" t="n">
+      <c r="F311" s="5" t="n">
         <v>-90.56999999999999</v>
       </c>
     </row>
@@ -12118,7 +12118,7 @@
       <c r="E312" s="3" t="n">
         <v>-1690</v>
       </c>
-      <c r="F312" s="6" t="n">
+      <c r="F312" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       <c r="E325" s="3" t="n">
         <v>-30</v>
       </c>
-      <c r="F325" s="6" t="n">
+      <c r="F325" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       <c r="E329" s="3" t="n">
         <v>-608</v>
       </c>
-      <c r="F329" s="6" t="n">
+      <c r="F329" s="5" t="n">
         <v>-57.58</v>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       <c r="E330" s="3" t="n">
         <v>-48</v>
       </c>
-      <c r="F330" s="6" t="n">
+      <c r="F330" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       <c r="E331" s="3" t="n">
         <v>-250</v>
       </c>
-      <c r="F331" s="6" t="n">
+      <c r="F331" s="5" t="n">
         <v>-13.31</v>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
       <c r="E333" s="3" t="n">
         <v>-2258</v>
       </c>
-      <c r="F333" s="6" t="n">
+      <c r="F333" s="5" t="n">
         <v>-46.35</v>
       </c>
     </row>
@@ -12694,7 +12694,7 @@
       <c r="E335" s="3" t="n">
         <v>-390</v>
       </c>
-      <c r="F335" s="6" t="n">
+      <c r="F335" s="5" t="n">
         <v>-46.43</v>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       <c r="E337" s="3" t="n">
         <v>-1310</v>
       </c>
-      <c r="F337" s="6" t="n">
+      <c r="F337" s="5" t="n">
         <v>-71.12</v>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       <c r="E338" s="3" t="n">
         <v>-2812</v>
       </c>
-      <c r="F338" s="6" t="n">
+      <c r="F338" s="5" t="n">
         <v>-52.27</v>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       <c r="E343" s="3" t="n">
         <v>-1599</v>
       </c>
-      <c r="F343" s="6" t="n">
+      <c r="F343" s="5" t="n">
         <v>-38.44</v>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       <c r="E344" s="3" t="n">
         <v>-3141</v>
       </c>
-      <c r="F344" s="6" t="n">
+      <c r="F344" s="5" t="n">
         <v>-53.4</v>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       <c r="E345" s="3" t="n">
         <v>-3248</v>
       </c>
-      <c r="F345" s="6" t="n">
+      <c r="F345" s="5" t="n">
         <v>-56.68</v>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       <c r="E346" s="3" t="n">
         <v>-101</v>
       </c>
-      <c r="F346" s="6" t="n">
+      <c r="F346" s="5" t="n">
         <v>-4.98</v>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       <c r="E347" s="3" t="n">
         <v>-2982</v>
       </c>
-      <c r="F347" s="6" t="n">
+      <c r="F347" s="5" t="n">
         <v>-87.70999999999999</v>
       </c>
     </row>
@@ -13006,7 +13006,7 @@
       <c r="E348" s="3" t="n">
         <v>-1284</v>
       </c>
-      <c r="F348" s="6" t="n">
+      <c r="F348" s="5" t="n">
         <v>-39.98</v>
       </c>
     </row>
@@ -13030,7 +13030,7 @@
       <c r="E349" s="3" t="n">
         <v>-765</v>
       </c>
-      <c r="F349" s="6" t="n">
+      <c r="F349" s="5" t="n">
         <v>-28.52</v>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       <c r="E354" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F354" s="5" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -13200,7 +13200,7 @@
       <c r="E356" s="3" t="n">
         <v>2146</v>
       </c>
-      <c r="F356" s="5" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -13274,7 +13274,7 @@
       <c r="E359" s="3" t="n">
         <v>-951</v>
       </c>
-      <c r="F359" s="6" t="n">
+      <c r="F359" s="5" t="n">
         <v>-44.25</v>
       </c>
     </row>
@@ -13298,7 +13298,7 @@
       <c r="E360" s="3" t="n">
         <v>-1730</v>
       </c>
-      <c r="F360" s="6" t="n">
+      <c r="F360" s="5" t="n">
         <v>-91.05</v>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       <c r="E361" s="3" t="n">
         <v>-1852</v>
       </c>
-      <c r="F361" s="6" t="n">
+      <c r="F361" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       <c r="E362" s="3" t="n">
         <v>-17462</v>
       </c>
-      <c r="F362" s="6" t="n">
+      <c r="F362" s="5" t="n">
         <v>-48.49</v>
       </c>
     </row>
@@ -13394,7 +13394,7 @@
       <c r="E364" s="3" t="n">
         <v>-6300</v>
       </c>
-      <c r="F364" s="6" t="n">
+      <c r="F364" s="5" t="n">
         <v>-19.26</v>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       <c r="E365" s="3" t="n">
         <v>-4532</v>
       </c>
-      <c r="F365" s="6" t="n">
+      <c r="F365" s="5" t="n">
         <v>-14.86</v>
       </c>
     </row>
@@ -13514,7 +13514,7 @@
       <c r="E369" s="3" t="n">
         <v>-1621</v>
       </c>
-      <c r="F369" s="6" t="n">
+      <c r="F369" s="5" t="n">
         <v>-4.53</v>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       <c r="E370" s="3" t="n">
         <v>-3061</v>
       </c>
-      <c r="F370" s="6" t="n">
+      <c r="F370" s="5" t="n">
         <v>-6.66</v>
       </c>
     </row>
@@ -13562,7 +13562,7 @@
       <c r="E371" s="3" t="n">
         <v>-4814</v>
       </c>
-      <c r="F371" s="6" t="n">
+      <c r="F371" s="5" t="n">
         <v>-17.91</v>
       </c>
     </row>
@@ -13586,7 +13586,7 @@
       <c r="E372" s="3" t="n">
         <v>-4104</v>
       </c>
-      <c r="F372" s="6" t="n">
+      <c r="F372" s="5" t="n">
         <v>-12.71</v>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       <c r="E374" s="3" t="n">
         <v>-18583</v>
       </c>
-      <c r="F374" s="6" t="n">
+      <c r="F374" s="5" t="n">
         <v>-60.58</v>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       <c r="E375" s="3" t="n">
         <v>-4163</v>
       </c>
-      <c r="F375" s="6" t="n">
+      <c r="F375" s="5" t="n">
         <v>-39.71</v>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       <c r="E376" s="3" t="n">
         <v>-22979</v>
       </c>
-      <c r="F376" s="6" t="n">
+      <c r="F376" s="5" t="n">
         <v>-68.88</v>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
       <c r="E377" s="3" t="n">
         <v>-6099</v>
       </c>
-      <c r="F377" s="6" t="n">
+      <c r="F377" s="5" t="n">
         <v>-32.68</v>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       <c r="E378" s="3" t="n">
         <v>-4083</v>
       </c>
-      <c r="F378" s="6" t="n">
+      <c r="F378" s="5" t="n">
         <v>-15.69</v>
       </c>
     </row>
@@ -13778,7 +13778,7 @@
       <c r="E380" s="3" t="n">
         <v>-12025</v>
       </c>
-      <c r="F380" s="6" t="n">
+      <c r="F380" s="5" t="n">
         <v>-9.98</v>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       <c r="E383" s="3" t="n">
         <v>-21870</v>
       </c>
-      <c r="F383" s="6" t="n">
+      <c r="F383" s="5" t="n">
         <v>-57.99</v>
       </c>
     </row>
@@ -13874,7 +13874,7 @@
       <c r="E384" s="3" t="n">
         <v>-31793</v>
       </c>
-      <c r="F384" s="6" t="n">
+      <c r="F384" s="5" t="n">
         <v>-71.98</v>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       <c r="E385" s="3" t="n">
         <v>-15887</v>
       </c>
-      <c r="F385" s="6" t="n">
+      <c r="F385" s="5" t="n">
         <v>-37.78</v>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       <c r="E386" s="3" t="n">
         <v>-7152</v>
       </c>
-      <c r="F386" s="6" t="n">
+      <c r="F386" s="5" t="n">
         <v>-3.24</v>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       <c r="E397" s="3" t="n">
         <v>-28168</v>
       </c>
-      <c r="F397" s="6" t="n">
+      <c r="F397" s="5" t="n">
         <v>-9.24</v>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       <c r="E398" s="3" t="n">
         <v>-10044</v>
       </c>
-      <c r="F398" s="6" t="n">
+      <c r="F398" s="5" t="n">
         <v>-7.57</v>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       <c r="E419" s="3" t="n">
         <v>-3656</v>
       </c>
-      <c r="F419" s="6" t="n">
+      <c r="F419" s="5" t="n">
         <v>-3.89</v>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -14835,7 +14835,7 @@
       <c r="D2" s="3" t="n">
         <v>-32564</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="5" t="n">
         <v>-2.31</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -15344,7 +15344,7 @@
       <c r="O3" s="3" t="n">
         <v>8466</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="5" t="n">
         <v>-28.31</v>
       </c>
     </row>
@@ -15446,7 +15446,7 @@
       <c r="O5" s="3" t="n">
         <v>520581</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="5" t="n">
         <v>-53</v>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       <c r="O9" s="3" t="n">
         <v>2032695</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="5" t="n">
         <v>-1.2</v>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       <c r="O11" s="3" t="n">
         <v>74514</v>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>∞ (新增/归零)</t>
         </is>
@@ -16060,7 +16060,7 @@
       <c r="O17" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="5" t="n">
         <v>-90.13</v>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       <c r="O21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -16366,7 +16366,7 @@
       <c r="O23" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="5" t="n">
         <v>-91.34999999999999</v>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       <c r="O25" s="3" t="n">
         <v>361499</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="5" t="n">
         <v>-17.54</v>
       </c>
     </row>
@@ -16774,7 +16774,7 @@
       <c r="O31" s="3" t="n">
         <v>66869</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="5" t="n">
         <v>-58.07</v>
       </c>
     </row>
@@ -16876,7 +16876,7 @@
       <c r="O33" s="3" t="n">
         <v>108977</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="5" t="n">
         <v>-15.61</v>
       </c>
     </row>
@@ -17182,7 +17182,7 @@
       <c r="O39" s="3" t="n">
         <v>578929</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="5" t="n">
         <v>-16.84</v>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       <c r="O41" s="3" t="n">
         <v>243848</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="5" t="n">
         <v>-45.9</v>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       <c r="O47" s="3" t="n">
         <v>12600</v>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="P47" s="5" t="n">
         <v>-47.15</v>
       </c>
     </row>
@@ -17896,7 +17896,7 @@
       <c r="O53" s="3" t="n">
         <v>12422</v>
       </c>
-      <c r="P53" s="6" t="n">
+      <c r="P53" s="5" t="n">
         <v>-31.65</v>
       </c>
     </row>
@@ -17998,7 +17998,7 @@
       <c r="O55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P55" s="6" t="n">
+      <c r="P55" s="5" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       <c r="O57" s="3" t="n">
         <v>21624</v>
       </c>
-      <c r="P57" s="6" t="n">
+      <c r="P57" s="5" t="n">
         <v>-5.75</v>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       <c r="O59" s="3" t="n">
         <v>32178</v>
       </c>
-      <c r="P59" s="6" t="n">
+      <c r="P59" s="5" t="n">
         <v>-18.09</v>
       </c>
     </row>
@@ -18406,7 +18406,7 @@
       <c r="O63" s="3" t="n">
         <v>377538</v>
       </c>
-      <c r="P63" s="6" t="n">
+      <c r="P63" s="5" t="n">
         <v>-4.88</v>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       <c r="O65" s="3" t="n">
         <v>441631</v>
       </c>
-      <c r="P65" s="6" t="n">
+      <c r="P65" s="5" t="n">
         <v>-12.72</v>
       </c>
     </row>
